--- a/Source_data/MMGBSA_calculation/MMGBSA_result.xlsx
+++ b/Source_data/MMGBSA_calculation/MMGBSA_result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Histone_core_cancer_mutation\Source_data\MMGBSA_calculation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3359FD-38A6-48F3-8883-B2AB6EDDB109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE096B1F-3658-40A3-8274-385CF9870F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4125" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{F462FE08-0CA4-49F3-92B8-12EBD180F88B}"/>
+    <workbookView xWindow="6600" yWindow="4545" windowWidth="28800" windowHeight="15345" xr2:uid="{F462FE08-0CA4-49F3-92B8-12EBD180F88B}"/>
   </bookViews>
   <sheets>
     <sheet name="mmgbsa" sheetId="1" r:id="rId1"/>
@@ -1152,18 +1152,18 @@
         <v>-125.2329</v>
       </c>
       <c r="D4" s="1">
-        <v>-134.17429999999999</v>
+        <v>-133.0643</v>
       </c>
       <c r="E4" s="1">
         <v>-129.9486</v>
       </c>
       <c r="F4" s="2">
         <f t="shared" si="0"/>
-        <v>-129.78526666666667</v>
+        <v>-129.41526666666667</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" si="1"/>
-        <v>2.5824514724923215</v>
+        <v>2.2764035833842042</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
@@ -1199,7 +1199,7 @@
         <v>19</v>
       </c>
       <c r="C6" s="1">
-        <v>-141.286</v>
+        <v>-141.06139999999999</v>
       </c>
       <c r="D6" s="1">
         <v>-138.57300000000001</v>
@@ -1209,11 +1209,11 @@
       </c>
       <c r="F6" s="2">
         <f t="shared" si="0"/>
-        <v>-142.56063333333336</v>
+        <v>-142.48576666666668</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" si="1"/>
-        <v>2.7452188803647526</v>
+        <v>2.7635591666866444</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
@@ -1424,21 +1424,21 @@
         <v>18</v>
       </c>
       <c r="C15" s="1">
-        <v>-55.4161</v>
+        <v>-54.740200000000002</v>
       </c>
       <c r="D15" s="1">
         <v>-66.006200000000007</v>
       </c>
       <c r="E15" s="1">
-        <v>-56.296500000000002</v>
+        <v>-57.4756</v>
       </c>
       <c r="F15" s="2">
         <f t="shared" si="0"/>
-        <v>-59.239600000000003</v>
+        <v>-59.407333333333334</v>
       </c>
       <c r="G15" s="3">
         <f t="shared" si="1"/>
-        <v>3.3928322834076767</v>
+        <v>3.3926088414538933</v>
       </c>
     </row>
   </sheetData>
